--- a/data/final/04_merged_crs_gsynth.xlsx
+++ b/data/final/04_merged_crs_gsynth.xlsx
@@ -394,19 +394,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.08567130189194984</v>
+        <v>-0.08567130189195106</v>
       </c>
       <c r="C2">
-        <v>0.1789242934416793</v>
+        <v>0.1714310405650292</v>
       </c>
       <c r="D2">
-        <v>0.06373999445408682</v>
+        <v>0.06264261961658707</v>
       </c>
       <c r="E2">
-        <v>-0.2105993953967427</v>
+        <v>-0.208448580237704</v>
       </c>
       <c r="F2">
-        <v>0.03925679161284307</v>
+        <v>0.03710597645380184</v>
       </c>
     </row>
     <row r="3">
@@ -416,19 +416,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.0856713018919501</v>
+        <v>-0.08567130189195042</v>
       </c>
       <c r="C3">
-        <v>0.1789242934416782</v>
+        <v>0.1714310405650319</v>
       </c>
       <c r="D3">
-        <v>0.06373999445408685</v>
+        <v>0.06264261961658701</v>
       </c>
       <c r="E3">
-        <v>-0.210599395396743</v>
+        <v>-0.2084485802377032</v>
       </c>
       <c r="F3">
-        <v>0.03925679161284286</v>
+        <v>0.03710597645380237</v>
       </c>
     </row>
     <row r="4">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.07874325761596483</v>
+        <v>-0.07874325761596515</v>
       </c>
       <c r="C4">
-        <v>0.2116982961052591</v>
+        <v>0.2153051554759084</v>
       </c>
       <c r="D4">
-        <v>0.06304962707444477</v>
+        <v>0.06354829254118555</v>
       </c>
       <c r="E4">
-        <v>-0.202318255920558</v>
+        <v>-0.2032956222757041</v>
       </c>
       <c r="F4">
-        <v>0.04483174068862836</v>
+        <v>0.04580910704377383</v>
       </c>
     </row>
     <row r="5">
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.07322514792062901</v>
+        <v>-0.07322514792062908</v>
       </c>
       <c r="C5">
-        <v>0.266538883853003</v>
+        <v>0.2754248388343639</v>
       </c>
       <c r="D5">
-        <v>0.06590516313199909</v>
+        <v>0.06713870680120824</v>
       </c>
       <c r="E5">
-        <v>-0.2023968940545842</v>
+        <v>-0.2048145952195916</v>
       </c>
       <c r="F5">
-        <v>0.05594659821332615</v>
+        <v>0.05836429937833341</v>
       </c>
     </row>
     <row r="6">
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.1307719482707323</v>
+        <v>-0.1307719482707332</v>
       </c>
       <c r="C6">
-        <v>0.03034443057423686</v>
+        <v>0.03008472901982784</v>
       </c>
       <c r="D6">
-        <v>0.0603869836179239</v>
+        <v>0.06029210343498578</v>
       </c>
       <c r="E6">
-        <v>-0.2491282612968734</v>
+        <v>-0.2489422995554689</v>
       </c>
       <c r="F6">
-        <v>-0.01241563524459123</v>
+        <v>-0.01260159698599739</v>
       </c>
     </row>
     <row r="7">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.1308646076437462</v>
+        <v>-0.1308646076437477</v>
       </c>
       <c r="C7">
-        <v>0.1267584937119797</v>
+        <v>0.1209469348713987</v>
       </c>
       <c r="D7">
-        <v>0.08569989518320711</v>
+        <v>0.08438461582231006</v>
       </c>
       <c r="E7">
-        <v>-0.2988333156816897</v>
+        <v>-0.2962554155047242</v>
       </c>
       <c r="F7">
-        <v>0.03710410039419737</v>
+        <v>0.03452620021722874</v>
       </c>
     </row>
     <row r="8">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1513931137107803</v>
+        <v>-0.1513931137107819</v>
       </c>
       <c r="C8">
-        <v>0.1236135136200545</v>
+        <v>0.1242674292241346</v>
       </c>
       <c r="D8">
-        <v>0.09832113819981315</v>
+        <v>0.0984923251903963</v>
       </c>
       <c r="E8">
-        <v>-0.3440990035013994</v>
+        <v>-0.3444345238375657</v>
       </c>
       <c r="F8">
-        <v>0.04131277607983869</v>
+        <v>0.04164829641600187</v>
       </c>
     </row>
     <row r="9">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1527033132426435</v>
+        <v>-0.1527033132426452</v>
       </c>
       <c r="C9">
-        <v>0.1219401982267048</v>
+        <v>0.1030741287579804</v>
       </c>
       <c r="D9">
-        <v>0.09872967850747097</v>
+        <v>0.0936755715746676</v>
       </c>
       <c r="E9">
-        <v>-0.3462099273225048</v>
+        <v>-0.3363040597601976</v>
       </c>
       <c r="F9">
-        <v>0.04080330083721775</v>
+        <v>0.03089743327490732</v>
       </c>
     </row>
     <row r="10">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.03905240257104436</v>
+        <v>-0.03905240257104454</v>
       </c>
       <c r="C10">
-        <v>0.5684351435673167</v>
+        <v>0.5694963340808505</v>
       </c>
       <c r="D10">
-        <v>0.06847002438588373</v>
+        <v>0.06865832222801464</v>
       </c>
       <c r="E10">
-        <v>-0.1732511843879557</v>
+        <v>-0.173620241376899</v>
       </c>
       <c r="F10">
-        <v>0.09514637924586694</v>
+        <v>0.09551543623480996</v>
       </c>
     </row>
     <row r="11">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.05677195561407844</v>
+        <v>-0.05677195561407858</v>
       </c>
       <c r="C11">
-        <v>0.3797332442838879</v>
+        <v>0.3766687405701934</v>
       </c>
       <c r="D11">
-        <v>0.06463198674020548</v>
+        <v>0.064217972160929</v>
       </c>
       <c r="E11">
-        <v>-0.1834483218741515</v>
+        <v>-0.1826368682096952</v>
       </c>
       <c r="F11">
-        <v>0.06990441064599459</v>
+        <v>0.06909295698153806</v>
       </c>
     </row>
     <row r="12">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.04559216237924049</v>
+        <v>-0.0455921623792408</v>
       </c>
       <c r="C12">
-        <v>0.4826971313016637</v>
+        <v>0.4757313361430815</v>
       </c>
       <c r="D12">
-        <v>0.06494876586513541</v>
+        <v>0.06392754678991359</v>
       </c>
       <c r="E12">
-        <v>-0.1728894043152303</v>
+        <v>-0.1708878517074705</v>
       </c>
       <c r="F12">
-        <v>0.08170507955674933</v>
+        <v>0.07970352694898894</v>
       </c>
     </row>
     <row r="13">
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.01603439683491302</v>
+        <v>-0.01603439683491326</v>
       </c>
       <c r="C13">
-        <v>0.8181237013636995</v>
+        <v>0.8185075773051933</v>
       </c>
       <c r="D13">
-        <v>0.06972722663327489</v>
+        <v>0.06987733166307081</v>
       </c>
       <c r="E13">
-        <v>-0.1526972497779938</v>
+        <v>-0.1529914502302923</v>
       </c>
       <c r="F13">
-        <v>0.1206284561081678</v>
+        <v>0.1209226565604658</v>
       </c>
     </row>
     <row r="14">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.1030902334534264</v>
+        <v>0.1030902334534263</v>
       </c>
       <c r="C14">
-        <v>0.06130154179642466</v>
+        <v>0.06726743002999358</v>
       </c>
       <c r="D14">
-        <v>0.05508975071699382</v>
+        <v>0.05633706154874878</v>
       </c>
       <c r="E14">
-        <v>-0.004883693869171035</v>
+        <v>-0.007328378176937586</v>
       </c>
       <c r="F14">
-        <v>0.2110641607760239</v>
+        <v>0.2135088450837902</v>
       </c>
     </row>
     <row r="15">
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.1543491662009741</v>
+        <v>0.1543491662009737</v>
       </c>
       <c r="C15">
-        <v>0.03133162415865876</v>
+        <v>0.03570877830294039</v>
       </c>
       <c r="D15">
-        <v>0.07169576122091847</v>
+        <v>0.07349161944316453</v>
       </c>
       <c r="E15">
-        <v>0.01382805636379045</v>
+        <v>0.01030823892684773</v>
       </c>
       <c r="F15">
-        <v>0.2948702760381576</v>
+        <v>0.2983900934750998</v>
       </c>
     </row>
     <row r="16">
@@ -705,16 +705,16 @@
         <v>0.1722714091809653</v>
       </c>
       <c r="C16">
-        <v>0.0345664025588317</v>
+        <v>0.02067106866284774</v>
       </c>
       <c r="D16">
-        <v>0.08151380357951185</v>
+        <v>0.07444941698297623</v>
       </c>
       <c r="E16">
-        <v>0.01250728992224998</v>
+        <v>0.02635323322432723</v>
       </c>
       <c r="F16">
-        <v>0.3320355284396806</v>
+        <v>0.3181895851376033</v>
       </c>
     </row>
     <row r="17">
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.1243499462382126</v>
+        <v>0.1243499462382125</v>
       </c>
       <c r="C17">
-        <v>0.03713146976224646</v>
+        <v>0.02980034243875873</v>
       </c>
       <c r="D17">
-        <v>0.05965984544944632</v>
+        <v>0.057232015343418</v>
       </c>
       <c r="E17">
-        <v>0.007418797834071997</v>
+        <v>0.01217725740246951</v>
       </c>
       <c r="F17">
-        <v>0.2412810946423531</v>
+        <v>0.2365226350739555</v>
       </c>
     </row>
     <row r="18">
@@ -746,19 +746,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.01108877439475097</v>
+        <v>0.01108877439475173</v>
       </c>
       <c r="C18">
-        <v>0.8840824339722348</v>
+        <v>0.8874930950439834</v>
       </c>
       <c r="D18">
-        <v>0.07605678085080884</v>
+        <v>0.07837861322827636</v>
       </c>
       <c r="E18">
-        <v>-0.13797977685289</v>
+        <v>-0.1425304846908645</v>
       </c>
       <c r="F18">
-        <v>0.1601573256423919</v>
+        <v>0.164708033480368</v>
       </c>
     </row>
     <row r="19">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.04431267815572942</v>
+        <v>0.04431267815572967</v>
       </c>
       <c r="C19">
-        <v>0.3689675011572318</v>
+        <v>0.4032688696351512</v>
       </c>
       <c r="D19">
-        <v>0.04932349804375366</v>
+        <v>0.0530184423766315</v>
       </c>
       <c r="E19">
-        <v>-0.05235960160155953</v>
+        <v>-0.05960155941888023</v>
       </c>
       <c r="F19">
-        <v>0.1409849579130184</v>
+        <v>0.1482269157303396</v>
       </c>
     </row>
     <row r="20">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.07807960370712359</v>
+        <v>0.07807960370712394</v>
       </c>
       <c r="C20">
-        <v>0.1003319717180484</v>
+        <v>0.1003636677900099</v>
       </c>
       <c r="D20">
-        <v>0.04751545821657919</v>
+        <v>0.04751988957779493</v>
       </c>
       <c r="E20">
-        <v>-0.01504898310628937</v>
+        <v>-0.01505766841467437</v>
       </c>
       <c r="F20">
-        <v>0.1712081905205365</v>
+        <v>0.1712168758289223</v>
       </c>
     </row>
     <row r="21">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.14427108094746</v>
+        <v>0.1442710809474586</v>
       </c>
       <c r="C21">
-        <v>0.02728963688514074</v>
+        <v>0.02569516820157114</v>
       </c>
       <c r="D21">
-        <v>0.0653594128199252</v>
+        <v>0.06467269597885884</v>
       </c>
       <c r="E21">
-        <v>0.01616898576972114</v>
+        <v>0.01751492604578689</v>
       </c>
       <c r="F21">
-        <v>0.2723731761251988</v>
+        <v>0.2710272358491302</v>
       </c>
     </row>
     <row r="22">
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.003003149728024531</v>
+        <v>-0.003003149728023146</v>
       </c>
       <c r="C22">
-        <v>0.9732993826602845</v>
+        <v>0.9722941884537057</v>
       </c>
       <c r="D22">
-        <v>0.08972524687962355</v>
+        <v>0.08646868750828896</v>
       </c>
       <c r="E22">
-        <v>-0.1788614021160515</v>
+        <v>-0.1724786630347179</v>
       </c>
       <c r="F22">
-        <v>0.1728551026600024</v>
+        <v>0.1664723635786716</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.04758973297018937</v>
+        <v>0.04758973297019638</v>
       </c>
       <c r="C23">
-        <v>0.4882216068347254</v>
+        <v>0.4870185831052734</v>
       </c>
       <c r="D23">
-        <v>0.0686581687188742</v>
+        <v>0.06846866364333112</v>
       </c>
       <c r="E23">
-        <v>-0.08697780496327856</v>
+        <v>-0.08660638184031959</v>
       </c>
       <c r="F23">
-        <v>0.1821572709036573</v>
+        <v>0.1817858477807123</v>
       </c>
     </row>
     <row r="24">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.05202735900597555</v>
+        <v>0.05202735900597241</v>
       </c>
       <c r="C24">
-        <v>0.4601999223783024</v>
+        <v>0.4493937536717771</v>
       </c>
       <c r="D24">
-        <v>0.07044835868102406</v>
+        <v>0.06878048996196108</v>
       </c>
       <c r="E24">
-        <v>-0.08604888677879122</v>
+        <v>-0.08277992415848998</v>
       </c>
       <c r="F24">
-        <v>0.1901036047907423</v>
+        <v>0.1868346421704348</v>
       </c>
     </row>
     <row r="25">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.09960736907507747</v>
+        <v>0.09960736907507721</v>
       </c>
       <c r="C25">
-        <v>0.08074096153946742</v>
+        <v>0.0623185073661594</v>
       </c>
       <c r="D25">
-        <v>0.0570357318351715</v>
+        <v>0.05343677711264495</v>
       </c>
       <c r="E25">
-        <v>-0.01218061115374323</v>
+        <v>-0.005126789515601124</v>
       </c>
       <c r="F25">
-        <v>0.2113953493038982</v>
+        <v>0.2043415276657555</v>
       </c>
     </row>
     <row r="26">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.06676993937617885</v>
+        <v>0.06676993937618518</v>
       </c>
       <c r="C26">
-        <v>0.2703499622041616</v>
+        <v>0.2842638334093448</v>
       </c>
       <c r="D26">
-        <v>0.06057565522559075</v>
+        <v>0.06235577012590569</v>
       </c>
       <c r="E26">
-        <v>-0.05195616320589451</v>
+        <v>-0.05544512429884856</v>
       </c>
       <c r="F26">
-        <v>0.1854960419582522</v>
+        <v>0.1889850030512189</v>
       </c>
     </row>
     <row r="27">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.03827005853609021</v>
+        <v>0.0382700585360927</v>
       </c>
       <c r="C27">
-        <v>0.5519036483346449</v>
+        <v>0.5556829748728107</v>
       </c>
       <c r="D27">
-        <v>0.06432915913582442</v>
+        <v>0.06494532303503801</v>
       </c>
       <c r="E27">
-        <v>-0.0878127765258714</v>
+        <v>-0.08902043557690131</v>
       </c>
       <c r="F27">
-        <v>0.1643528935980518</v>
+        <v>0.1655605526490867</v>
       </c>
     </row>
     <row r="28">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.04947319706348902</v>
+        <v>0.04947319706348759</v>
       </c>
       <c r="C28">
-        <v>0.2524728912819436</v>
+        <v>0.2232196696951585</v>
       </c>
       <c r="D28">
-        <v>0.04323206236125589</v>
+        <v>0.04061801077468365</v>
       </c>
       <c r="E28">
-        <v>-0.03526008814196214</v>
+        <v>-0.0301366411785522</v>
       </c>
       <c r="F28">
-        <v>0.1342064822689402</v>
+        <v>0.1290830353055274</v>
       </c>
     </row>
     <row r="29">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.0947381218745027</v>
+        <v>0.09473812187450248</v>
       </c>
       <c r="C29">
-        <v>0.1263640208440739</v>
+        <v>0.1379812961428288</v>
       </c>
       <c r="D29">
-        <v>0.06197711502066656</v>
+        <v>0.06386765511560973</v>
       </c>
       <c r="E29">
-        <v>-0.02673479143170011</v>
+        <v>-0.03044018192911788</v>
       </c>
       <c r="F29">
-        <v>0.2162110351807055</v>
+        <v>0.2199164256781228</v>
       </c>
     </row>
     <row r="30">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.0370219059448027</v>
+        <v>0.03702190594480945</v>
       </c>
       <c r="C30">
-        <v>0.5805621367265965</v>
+        <v>0.6059086163558578</v>
       </c>
       <c r="D30">
-        <v>0.06700023786220539</v>
+        <v>0.07175867291166095</v>
       </c>
       <c r="E30">
-        <v>-0.09429614722073673</v>
+        <v>-0.1036225085404359</v>
       </c>
       <c r="F30">
-        <v>0.1683399591103421</v>
+        <v>0.1776663204300548</v>
       </c>
     </row>
     <row r="31">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.1312510179015908</v>
+        <v>-0.1312510179015874</v>
       </c>
       <c r="C31">
-        <v>0.08786184058132429</v>
+        <v>0.07969021586186797</v>
       </c>
       <c r="D31">
-        <v>0.07689951756982467</v>
+        <v>0.07489417437605167</v>
       </c>
       <c r="E31">
-        <v>-0.2819713027669522</v>
+        <v>-0.2780409023305112</v>
       </c>
       <c r="F31">
-        <v>0.0194692669637706</v>
+        <v>0.01553886652733638</v>
       </c>
     </row>
     <row r="32">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.05841060427978059</v>
+        <v>-0.05841060427978112</v>
       </c>
       <c r="C32">
-        <v>0.4259116657683331</v>
+        <v>0.4204552786573728</v>
       </c>
       <c r="D32">
-        <v>0.07336106844652576</v>
+        <v>0.07250286813946118</v>
       </c>
       <c r="E32">
-        <v>-0.2021956563023488</v>
+        <v>-0.2005136146089815</v>
       </c>
       <c r="F32">
-        <v>0.08537444774278763</v>
+        <v>0.0836924060494193</v>
       </c>
     </row>
     <row r="33">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.07227870423637023</v>
+        <v>-0.07227870423636776</v>
       </c>
       <c r="C33">
-        <v>0.2397507247567758</v>
+        <v>0.2364430811198532</v>
       </c>
       <c r="D33">
-        <v>0.06148186828791295</v>
+        <v>0.06105011284592253</v>
       </c>
       <c r="E33">
-        <v>-0.1927809517829149</v>
+        <v>-0.191934726666482</v>
       </c>
       <c r="F33">
-        <v>0.04822354331017439</v>
+        <v>0.04737731819374646</v>
       </c>
     </row>
     <row r="34">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.02778217614866319</v>
+        <v>-0.02778217614866032</v>
       </c>
       <c r="C34">
-        <v>0.6719318312081799</v>
+        <v>0.6550728698521171</v>
       </c>
       <c r="D34">
-        <v>0.06560164344318727</v>
+        <v>0.06219063355931509</v>
       </c>
       <c r="E34">
-        <v>-0.1563590346239484</v>
+        <v>-0.1496735781006459</v>
       </c>
       <c r="F34">
-        <v>0.100794682326622</v>
+        <v>0.09410922580332526</v>
       </c>
     </row>
     <row r="35">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.0605696585633585</v>
+        <v>0.06056965856335989</v>
       </c>
       <c r="C35">
-        <v>0.4104050332368494</v>
+        <v>0.3992111056204264</v>
       </c>
       <c r="D35">
-        <v>0.07357999462865294</v>
+        <v>0.07184748656541458</v>
       </c>
       <c r="E35">
-        <v>-0.08364448089145185</v>
+        <v>-0.08024882748457804</v>
       </c>
       <c r="F35">
-        <v>0.2047837980181688</v>
+        <v>0.2013881446112978</v>
       </c>
     </row>
     <row r="36">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.04634023427191756</v>
+        <v>-0.04634023427191482</v>
       </c>
       <c r="C36">
-        <v>0.5058665553204642</v>
+        <v>0.4827726875414817</v>
       </c>
       <c r="D36">
-        <v>0.06965443778822518</v>
+        <v>0.06602583393025376</v>
       </c>
       <c r="E36">
-        <v>-0.1828604237002247</v>
+        <v>-0.1757484908244348</v>
       </c>
       <c r="F36">
-        <v>0.09017995515638955</v>
+        <v>0.08306802228060518</v>
       </c>
     </row>
     <row r="37">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.05686590354112924</v>
+        <v>-0.05686590354113046</v>
       </c>
       <c r="C37">
-        <v>0.3456516673268171</v>
+        <v>0.3679452931382232</v>
       </c>
       <c r="D37">
-        <v>0.06029953012146739</v>
+        <v>0.06316126159054067</v>
       </c>
       <c r="E37">
-        <v>-0.1750508108638934</v>
+        <v>-0.1806597014767032</v>
       </c>
       <c r="F37">
-        <v>0.06131900378163496</v>
+        <v>0.06692789439444224</v>
       </c>
     </row>
     <row r="38">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.02957485900099191</v>
+        <v>-0.02957485900099566</v>
       </c>
       <c r="C38">
-        <v>0.5131612345303733</v>
+        <v>0.521890090944086</v>
       </c>
       <c r="D38">
-        <v>0.0452268024348084</v>
+        <v>0.04617935811669834</v>
       </c>
       <c r="E38">
-        <v>-0.1182177629091248</v>
+        <v>-0.1200847377389018</v>
       </c>
       <c r="F38">
-        <v>0.05906804490714095</v>
+        <v>0.06093501973691046</v>
       </c>
     </row>
     <row r="39">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.06483586671400272</v>
+        <v>0.06483586671400711</v>
       </c>
       <c r="C39">
-        <v>0.1504075396595619</v>
+        <v>0.1597603080933001</v>
       </c>
       <c r="D39">
-        <v>0.04508459900411906</v>
+        <v>0.04611769969355976</v>
       </c>
       <c r="E39">
-        <v>-0.02352832359150098</v>
+        <v>-0.02555316373520387</v>
       </c>
       <c r="F39">
-        <v>0.1532000570195064</v>
+        <v>0.1552248971632181</v>
       </c>
     </row>
     <row r="40">
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.03423973883909499</v>
+        <v>-0.03423973883909705</v>
       </c>
       <c r="C40">
-        <v>0.6220626711610704</v>
+        <v>0.6112179016528256</v>
       </c>
       <c r="D40">
-        <v>0.06946178971711124</v>
+        <v>0.06735654286813597</v>
       </c>
       <c r="E40">
-        <v>-0.1703823449863276</v>
+        <v>-0.1662561369837717</v>
       </c>
       <c r="F40">
-        <v>0.1019028673081377</v>
+        <v>0.09777665930557765</v>
       </c>
     </row>
     <row r="41">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.04595571511773289</v>
+        <v>0.04595571511773626</v>
       </c>
       <c r="C41">
-        <v>0.4958793669062782</v>
+        <v>0.4984685541489178</v>
       </c>
       <c r="D41">
-        <v>0.06748392826381185</v>
+        <v>0.06789130473426996</v>
       </c>
       <c r="E41">
-        <v>-0.0863103538146229</v>
+        <v>-0.0871087970248665</v>
       </c>
       <c r="F41">
-        <v>0.1782217840500887</v>
+        <v>0.179020227260339</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.0478810975375315</v>
+        <v>0.04788109753754507</v>
       </c>
       <c r="C42">
-        <v>0.6197304771397996</v>
+        <v>0.6232669527748864</v>
       </c>
       <c r="D42">
-        <v>0.09648926729442364</v>
+        <v>0.09747274076320736</v>
       </c>
       <c r="E42">
-        <v>-0.1412343912541973</v>
+        <v>-0.1431619638327505</v>
       </c>
       <c r="F42">
-        <v>0.2369965863292603</v>
+        <v>0.2389241589078407</v>
       </c>
     </row>
     <row r="43">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.07374850425566963</v>
+        <v>0.07374850425566014</v>
       </c>
       <c r="C43">
-        <v>0.4859997180167048</v>
+        <v>0.5040048399055084</v>
       </c>
       <c r="D43">
-        <v>0.1058562554790661</v>
+        <v>0.1103686243722835</v>
       </c>
       <c r="E43">
-        <v>-0.1337259440215706</v>
+        <v>-0.1425700245372451</v>
       </c>
       <c r="F43">
-        <v>0.2812229525329099</v>
+        <v>0.2900670330485654</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.08961127881028923</v>
+        <v>0.08961127881027794</v>
       </c>
       <c r="C44">
-        <v>0.3630249262701823</v>
+        <v>0.3595533059853238</v>
       </c>
       <c r="D44">
-        <v>0.09851547717871406</v>
+        <v>0.09780578066695639</v>
       </c>
       <c r="E44">
-        <v>-0.1034755083797679</v>
+        <v>-0.1020845287767804</v>
       </c>
       <c r="F44">
-        <v>0.2826980660003464</v>
+        <v>0.2813070863973363</v>
       </c>
     </row>
     <row r="45">
@@ -1340,19 +1340,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.02768174720194629</v>
+        <v>-0.02768174720194</v>
       </c>
       <c r="C45">
-        <v>0.7357114572785384</v>
+        <v>0.74437296929847</v>
       </c>
       <c r="D45">
-        <v>0.08201078563591338</v>
+        <v>0.08489564800308289</v>
       </c>
       <c r="E45">
-        <v>-0.1884199333921713</v>
+        <v>-0.1940741597321722</v>
       </c>
       <c r="F45">
-        <v>0.1330564389882787</v>
+        <v>0.1387106653282922</v>
       </c>
     </row>
     <row r="46">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.05617714274579978</v>
+        <v>-0.05617714274581331</v>
       </c>
       <c r="C46">
-        <v>0.4131876435213966</v>
+        <v>0.4218362872235959</v>
       </c>
       <c r="D46">
-        <v>0.06865129131400514</v>
+        <v>0.06993821757415725</v>
       </c>
       <c r="E46">
-        <v>-0.1907312012134172</v>
+        <v>-0.1932535303340877</v>
       </c>
       <c r="F46">
-        <v>0.07837691572181771</v>
+        <v>0.08089924484246111</v>
       </c>
     </row>
     <row r="47">
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.1221550971742857</v>
+        <v>0.1221550971742643</v>
       </c>
       <c r="C47">
-        <v>0.253934490331132</v>
+        <v>0.2210894649169277</v>
       </c>
       <c r="D47">
-        <v>0.1070742410794053</v>
+        <v>0.09982958058025246</v>
       </c>
       <c r="E47">
-        <v>-0.08770655901330782</v>
+        <v>-0.07350728535476961</v>
       </c>
       <c r="F47">
-        <v>0.3320167533618793</v>
+        <v>0.3178174797032983</v>
       </c>
     </row>
     <row r="48">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.01953389354478819</v>
+        <v>0.01953389354478166</v>
       </c>
       <c r="C48">
-        <v>0.8245766637221295</v>
+        <v>0.816460445965064</v>
       </c>
       <c r="D48">
-        <v>0.08812450449883381</v>
+        <v>0.08416158767201067</v>
       </c>
       <c r="E48">
-        <v>-0.153186961428364</v>
+        <v>-0.1454197871740694</v>
       </c>
       <c r="F48">
-        <v>0.1922547485179404</v>
+        <v>0.1844875742636327</v>
       </c>
     </row>
     <row r="49">
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.09394129014224581</v>
+        <v>0.09394129014226457</v>
       </c>
       <c r="C49">
-        <v>0.301508310155262</v>
+        <v>0.286070724057073</v>
       </c>
       <c r="D49">
-        <v>0.0909222812155049</v>
+        <v>0.0880605175636333</v>
       </c>
       <c r="E49">
-        <v>-0.08426310643236642</v>
+        <v>-0.0786541527424135</v>
       </c>
       <c r="F49">
-        <v>0.272145686716858</v>
+        <v>0.2665367330269426</v>
       </c>
     </row>
     <row r="50">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.07445653998974557</v>
+        <v>-0.07445653998974308</v>
       </c>
       <c r="C50">
-        <v>0.46025099367353</v>
+        <v>0.4826831190160603</v>
       </c>
       <c r="D50">
-        <v>0.1008303772321943</v>
+        <v>0.1060644056008256</v>
       </c>
       <c r="E50">
-        <v>-0.2720804479124338</v>
+        <v>-0.2823389550090096</v>
       </c>
       <c r="F50">
-        <v>0.1231673679329427</v>
+        <v>0.1334258750295235</v>
       </c>
     </row>
     <row r="51">
@@ -1472,19 +1472,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.03928028570045396</v>
+        <v>0.0392802857004404</v>
       </c>
       <c r="C51">
-        <v>0.6696580966734778</v>
+        <v>0.6749495895715834</v>
       </c>
       <c r="D51">
-        <v>0.09207382335041436</v>
+        <v>0.0936661622039572</v>
       </c>
       <c r="E51">
-        <v>-0.1411810919852612</v>
+        <v>-0.1443020187894025</v>
       </c>
       <c r="F51">
-        <v>0.2197416633861691</v>
+        <v>0.2228625901902833</v>
       </c>
     </row>
     <row r="52">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.06183938357534999</v>
+        <v>-0.0618393835753248</v>
       </c>
       <c r="C52">
-        <v>0.6416593765242999</v>
+        <v>0.6456958946422242</v>
       </c>
       <c r="D52">
-        <v>0.1328793410715003</v>
+        <v>0.134506633060291</v>
       </c>
       <c r="E52">
-        <v>-0.3222781063649045</v>
+        <v>-0.3254675400552397</v>
       </c>
       <c r="F52">
-        <v>0.1985993392142045</v>
+        <v>0.2017887729045901</v>
       </c>
     </row>
     <row r="53">
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.07348939524015063</v>
+        <v>-0.07348939524015283</v>
       </c>
       <c r="C53">
-        <v>0.4271548756017134</v>
+        <v>0.4114441976138874</v>
       </c>
       <c r="D53">
-        <v>0.09254779318886008</v>
+        <v>0.08947338542611451</v>
       </c>
       <c r="E53">
-        <v>-0.2548797367389777</v>
+        <v>-0.2488540082502081</v>
       </c>
       <c r="F53">
-        <v>0.1079009462586764</v>
+        <v>0.1018752177699025</v>
       </c>
     </row>
     <row r="54">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.3110780154075357</v>
+        <v>-0.3110780154075568</v>
       </c>
       <c r="C54">
-        <v>0.2055011618547871</v>
+        <v>0.263257267118107</v>
       </c>
       <c r="D54">
-        <v>0.2457107694994441</v>
+        <v>0.2780646531121473</v>
       </c>
       <c r="E54">
-        <v>-0.7926622742400689</v>
+        <v>-0.8560747208809887</v>
       </c>
       <c r="F54">
-        <v>0.1705062434249975</v>
+        <v>0.2339186900658752</v>
       </c>
     </row>
     <row r="55">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.8120258238696957</v>
+        <v>-0.8120258238697518</v>
       </c>
       <c r="C55">
-        <v>0.248082365372903</v>
+        <v>0.2520024987313405</v>
       </c>
       <c r="D55">
-        <v>0.703040679142066</v>
+        <v>0.7088839060782853</v>
       </c>
       <c r="E55">
-        <v>-2.189960234654725</v>
+        <v>-2.201412749003265</v>
       </c>
       <c r="F55">
-        <v>0.5659085869153332</v>
+        <v>0.5773611012637614</v>
       </c>
     </row>
     <row r="56">
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.8525408849363622</v>
+        <v>-0.8525408849364655</v>
       </c>
       <c r="C56">
-        <v>0.366390196544532</v>
+        <v>0.3614523306342536</v>
       </c>
       <c r="D56">
-        <v>0.9438533020115532</v>
+        <v>0.9341877903846301</v>
       </c>
       <c r="E56">
-        <v>-2.702459363568212</v>
+        <v>-2.683515308887393</v>
       </c>
       <c r="F56">
-        <v>0.997377593695488</v>
+        <v>0.9784335390144623</v>
       </c>
     </row>
     <row r="57">
@@ -1604,19 +1604,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.7158805487575852</v>
+        <v>-0.7158805487576647</v>
       </c>
       <c r="C57">
-        <v>0.4887970180830361</v>
+        <v>0.4810771351226759</v>
       </c>
       <c r="D57">
-        <v>1.034175532235431</v>
+        <v>1.016051412288492</v>
       </c>
       <c r="E57">
-        <v>-2.742827345631571</v>
+        <v>-2.707304723284166</v>
       </c>
       <c r="F57">
-        <v>1.3110662481164</v>
+        <v>1.275543625768837</v>
       </c>
     </row>
     <row r="58">
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.9688891955279133</v>
+        <v>-0.9688891955280113</v>
       </c>
       <c r="C58">
-        <v>0.380667199731026</v>
+        <v>0.3591633973613937</v>
       </c>
       <c r="D58">
-        <v>1.105195600617662</v>
+        <v>1.056631461290923</v>
       </c>
       <c r="E58">
-        <v>-3.135032768610643</v>
+        <v>-3.039848804590148</v>
       </c>
       <c r="F58">
-        <v>1.197254377554816</v>
+        <v>1.102070413534125</v>
       </c>
     </row>
     <row r="59">
@@ -1648,19 +1648,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>-1.123676324208658</v>
+        <v>-1.123676324208753</v>
       </c>
       <c r="C59">
-        <v>0.3324155168309122</v>
+        <v>0.3150339048380755</v>
       </c>
       <c r="D59">
-        <v>1.159313709920349</v>
+        <v>1.118402595341744</v>
       </c>
       <c r="E59">
-        <v>-3.395889442436056</v>
+        <v>-3.315705131294695</v>
       </c>
       <c r="F59">
-        <v>1.14853679401874</v>
+        <v>1.06835248287719</v>
       </c>
     </row>
     <row r="60">
@@ -1670,19 +1670,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.9483619682314848</v>
+        <v>-0.9483619682315906</v>
       </c>
       <c r="C60">
-        <v>0.3871177995214397</v>
+        <v>0.3724358816956996</v>
       </c>
       <c r="D60">
-        <v>1.09655469463154</v>
+        <v>1.063281575535741</v>
       </c>
       <c r="E60">
-        <v>-3.097569676787619</v>
+        <v>-3.032355561706648</v>
       </c>
       <c r="F60">
-        <v>1.20084574032465</v>
+        <v>1.135631625243466</v>
       </c>
     </row>
     <row r="61">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.9397945402352386</v>
+        <v>-0.9397945402353264</v>
       </c>
       <c r="C61">
-        <v>0.4137868795417541</v>
+        <v>0.3918935695138219</v>
       </c>
       <c r="D61">
-        <v>1.149950648759057</v>
+        <v>1.097649213275433</v>
       </c>
       <c r="E61">
-        <v>-3.193656395801459</v>
+        <v>-3.091147465913898</v>
       </c>
       <c r="F61">
-        <v>1.314067315330982</v>
+        <v>1.211558385443246</v>
       </c>
     </row>
     <row r="62">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>-1.006493354554776</v>
+        <v>-1.006493354554914</v>
       </c>
       <c r="C62">
-        <v>0.3997516390636171</v>
+        <v>0.380143443341155</v>
       </c>
       <c r="D62">
-        <v>1.195268179894196</v>
+        <v>1.146828425067726</v>
       </c>
       <c r="E62">
-        <v>-3.349175939014143</v>
+        <v>-3.254235764134448</v>
       </c>
       <c r="F62">
-        <v>1.33618922990459</v>
+        <v>1.241249055024621</v>
       </c>
     </row>
     <row r="63">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>-1.172053636833486</v>
+        <v>-1.172053636833639</v>
       </c>
       <c r="C63">
-        <v>0.3183749618663809</v>
+        <v>0.2940518706008726</v>
       </c>
       <c r="D63">
-        <v>1.174634470292101</v>
+        <v>1.117013528080032</v>
       </c>
       <c r="E63">
-        <v>-3.474294893605286</v>
+        <v>-3.361359922114522</v>
       </c>
       <c r="F63">
-        <v>1.130187619938314</v>
+        <v>1.017252648447244</v>
       </c>
     </row>
     <row r="64">
@@ -1758,19 +1758,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>-1.246172681121854</v>
+        <v>-1.246172681121966</v>
       </c>
       <c r="C64">
-        <v>0.3137760626185075</v>
+        <v>0.2823975663265874</v>
       </c>
       <c r="D64">
-        <v>1.237104307068688</v>
+        <v>1.1592854094061</v>
       </c>
       <c r="E64">
-        <v>-3.670852568095863</v>
+        <v>-3.518330331360693</v>
       </c>
       <c r="F64">
-        <v>1.178507205852154</v>
+        <v>1.025984969116762</v>
       </c>
     </row>
     <row r="65">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.7147947414711561</v>
+        <v>-0.7147947414711878</v>
       </c>
       <c r="C65">
-        <v>0.3251161596118695</v>
+        <v>0.3028279151879607</v>
       </c>
       <c r="D65">
-        <v>0.7264183911853297</v>
+        <v>0.6937141716300643</v>
       </c>
       <c r="E65">
-        <v>-2.13854862590193</v>
+        <v>-2.074449533431151</v>
       </c>
       <c r="F65">
-        <v>0.7089591429596179</v>
+        <v>0.6448600504887755</v>
       </c>
     </row>
     <row r="66">
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.8990089800775758</v>
+        <v>-0.8990089800776662</v>
       </c>
       <c r="C2">
-        <v>0.3509561323243271</v>
+        <v>0.3344909562948124</v>
       </c>
       <c r="D2">
-        <v>0.9638404445750333</v>
+        <v>0.9315117260170717</v>
       </c>
       <c r="E2">
-        <v>-2.788101538287715</v>
+        <v>-2.724738414247868</v>
       </c>
       <c r="F2">
-        <v>0.990083578132563</v>
+        <v>0.9267204540925362</v>
       </c>
     </row>
   </sheetData>
